--- a/samples/stock_count/재고실사_부산물류센터.xlsx
+++ b/samples/stock_count/재고실사_부산물류센터.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>한지민</t>
+          <t>오민재</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>한지민</t>
+          <t>오민재</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>한지민</t>
+          <t>오민재</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>한지민</t>
+          <t>오민재</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>한지민</t>
+          <t>오민재</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>한지민</t>
+          <t>오민재</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>한지민</t>
+          <t>오민재</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>정우성</t>
+          <t>윤서진</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>정우성</t>
+          <t>윤서진</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>한지민</t>
+          <t>오민재</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>정우성</t>
+          <t>윤서진</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>정우성</t>
+          <t>윤서진</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>한지민</t>
+          <t>오민재</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>한지민</t>
+          <t>오민재</t>
         </is>
       </c>
     </row>
